--- a/5/search/FY2_Missile1_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY2_Missile1_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>296.2</v>
+        <v>295.4</v>
       </c>
       <c r="C3" t="n">
-        <v>118.1</v>
+        <v>116.6</v>
       </c>
       <c r="D3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>3.900000000000002</v>
+        <v>4.000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY2_Missile1_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY2_Missile1_results/fine_tuned/comparison.xlsx
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>297</v>
+        <v>274.5</v>
       </c>
       <c r="C2" t="n">
-        <v>117.6</v>
+        <v>136</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>3.800000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>295.4</v>
+        <v>285.6</v>
       </c>
       <c r="C3" t="n">
-        <v>116.6</v>
+        <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="F3" t="n">
         <v>4.000000000000002</v>
